--- a/Donnees/Statisiques Environnementales et de la  gouvernace/Gouvernance/Theme_Gouvernance (4).xlsx
+++ b/Donnees/Statisiques Environnementales et de la  gouvernace/Gouvernance/Theme_Gouvernance (4).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statisiques Environnementales et de la  gouvernace\Gouvernance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E568B91D-C7BF-402F-B6BE-B9DA1AE0433B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B6554F-F55E-42CE-B33F-D44D81672971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TSN1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="184">
   <si>
     <t>Année</t>
   </si>
@@ -98,21 +98,12 @@
     <t>2020~Nombre de crime meurtrier</t>
   </si>
   <si>
-    <t>2020~ Taux d'homicide(pour 100000 habitants)</t>
-  </si>
-  <si>
     <t>2021~Nombre de crime meurtrier</t>
   </si>
   <si>
-    <t>2021~ Taux d'homicide(pour 100000 habitants)</t>
-  </si>
-  <si>
     <t>2022~Nombre de crime meurtrier</t>
   </si>
   <si>
-    <t>2022~  Taux d'homicide(pour 100000 habitants)</t>
-  </si>
-  <si>
     <t>2023~ Nombre de crime meurtrier</t>
   </si>
   <si>
@@ -317,9 +308,6 @@
     <t>Tableau 3.2.13:  Efficacité du système judiciaire en Mauritanie  2010-2024</t>
   </si>
   <si>
-    <t>Tableau 3.2.14: Evolution du taux d'occupation par  prison  2020 - 2024</t>
-  </si>
-  <si>
     <t>Tableau 3.2.15:  Pourcentage de la population féminine carcérale  en Mauritanie  2010-2024</t>
   </si>
   <si>
@@ -344,9 +332,6 @@
     <t>15+</t>
   </si>
   <si>
-    <t>Tableau 3.2.5 : Evolution du nombre de réfugiés en Mauritanie par groupe d'âge (années)  2019-2024</t>
-  </si>
-  <si>
     <t>Source: Direction Générale de la Sûreté Nationale</t>
   </si>
   <si>
@@ -582,6 +567,30 @@
   </si>
   <si>
     <t>Nombre de femmes détenues</t>
+  </si>
+  <si>
+    <t>Source: https://data.unhcr.org/fr/country/mrt</t>
+  </si>
+  <si>
+    <t>Tableau 3.2.5 : Evolution du nombre de réfugiés en Mauritanie par groupe d'âge   2019-2024</t>
+  </si>
+  <si>
+    <t>2024~Nombre de crime meurtrier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Taux (%)</t>
+  </si>
+  <si>
+    <t>Tableau 3.2.14: Evolution du  taux (%) d'occupation par  prison  2020 - 2024</t>
+  </si>
+  <si>
+    <t>2020~Taux d'homicide(pour 100000 habitants)</t>
+  </si>
+  <si>
+    <t>2021~Taux d'homicide(pour 100000 habitants)</t>
+  </si>
+  <si>
+    <t>2022~ Taux d'homicide(pour 100000 habitants)</t>
   </si>
 </sst>
 </file>
@@ -592,7 +601,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,6 +680,24 @@
     <font>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <name val="Sakkal Majalla"/>
     </font>
   </fonts>
@@ -841,7 +868,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -993,6 +1020,24 @@
     </xf>
     <xf numFmtId="1" fontId="9" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1303,7 +1348,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1354,7 +1399,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -1375,71 +1420,71 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="K2" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="22" t="s">
+      <c r="L2" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="N2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" s="22" t="s">
+      <c r="O2" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="P2" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q2" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="M2" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="N2" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="P2" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q2" s="22" t="s">
-        <v>53</v>
-      </c>
       <c r="R2" s="23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="S2" s="22" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B3" s="10">
         <v>760</v>
@@ -1489,7 +1534,7 @@
     </row>
     <row r="4" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B4" s="10">
         <v>102</v>
@@ -1539,7 +1584,7 @@
     </row>
     <row r="5" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B5" s="10">
         <v>413</v>
@@ -1595,7 +1640,7 @@
     </row>
     <row r="6" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="10">
         <v>589</v>
@@ -1649,7 +1694,7 @@
     </row>
     <row r="7" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B7" s="10">
         <v>24</v>
@@ -1703,7 +1748,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1736,62 +1781,62 @@
   <sheetData>
     <row r="1" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="26" t="s">
+      <c r="I2" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="L2" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="M2" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="N2" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="K2" s="26" t="s">
+      <c r="O2" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="P2" s="26" t="s">
         <v>150</v>
-      </c>
-      <c r="L2" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="N2" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="O2" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="P2" s="26" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="27" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A3" s="33" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B3" s="34">
         <v>1244</v>
@@ -1841,7 +1886,7 @@
     </row>
     <row r="4" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B4" s="14">
         <v>553</v>
@@ -1894,7 +1939,7 @@
     </row>
     <row r="5" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B5" s="14">
         <v>81</v>
@@ -1947,7 +1992,7 @@
     </row>
     <row r="6" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B6" s="14">
         <v>278</v>
@@ -2000,7 +2045,7 @@
     </row>
     <row r="7" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B7" s="14">
         <v>254</v>
@@ -2053,7 +2098,7 @@
     </row>
     <row r="8" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B8" s="18">
         <v>16</v>
@@ -2106,7 +2151,7 @@
     </row>
     <row r="9" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B9" s="14">
         <v>62</v>
@@ -2125,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H9" s="14">
         <v>0</v>
@@ -2134,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
@@ -2145,7 +2190,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2164,71 +2209,71 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="I2" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="43" t="s">
+      <c r="L2" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="M2" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="43" t="s">
+      <c r="O2" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="P2" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>162</v>
-      </c>
-      <c r="J2" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="M2" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="O2" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="P2" s="43" t="s">
+      <c r="R2" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="S2" s="43" t="s">
         <v>40</v>
-      </c>
-      <c r="Q2" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="R2" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="S2" s="43" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="52" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B3" s="53">
         <f>SUM(B4:B8)</f>
@@ -2302,7 +2347,7 @@
     </row>
     <row r="4" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="45" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B4" s="46">
         <v>403</v>
@@ -2366,7 +2411,7 @@
     </row>
     <row r="5" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="45" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B5" s="46">
         <v>78</v>
@@ -2430,7 +2475,7 @@
     </row>
     <row r="6" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="45" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B6" s="46">
         <v>275</v>
@@ -2494,7 +2539,7 @@
     </row>
     <row r="7" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="45" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B7" s="46">
         <v>418</v>
@@ -2558,7 +2603,7 @@
     </row>
     <row r="8" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="45" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B8" s="50">
         <v>9</v>
@@ -2622,7 +2667,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2640,7 +2685,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2665,7 +2710,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B3">
         <v>700</v>
@@ -2685,7 +2730,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B4">
         <v>1700</v>
@@ -2705,7 +2750,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B5">
         <v>41.2</v>
@@ -2725,7 +2770,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2743,7 +2788,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2766,12 +2811,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>186.28</v>
@@ -2791,7 +2851,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B5">
         <v>60</v>
@@ -2811,7 +2871,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B6">
         <v>40</v>
@@ -2831,7 +2891,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>70.150000000000006</v>
@@ -2851,7 +2911,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B8">
         <v>87.33</v>
@@ -2871,7 +2931,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2889,12 +2949,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
@@ -2914,7 +2974,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B3">
         <v>1700</v>
@@ -2934,7 +2994,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B4">
         <v>62</v>
@@ -2954,7 +3014,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5">
         <v>3.6470588235294099</v>
@@ -2974,7 +3034,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2993,7 +3053,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -3001,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -3012,7 +3072,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>1328168</v>
@@ -3026,7 +3086,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B4">
         <v>2957</v>
@@ -3040,7 +3100,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <v>749865</v>
@@ -3054,7 +3114,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>33200</v>
@@ -3068,7 +3128,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>10877</v>
@@ -3082,7 +3142,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8">
         <v>705788</v>
@@ -3096,7 +3156,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B9">
         <v>56.5</v>
@@ -3110,7 +3170,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3129,24 +3189,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B3">
         <v>147</v>
@@ -3160,7 +3220,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B4">
         <v>37</v>
@@ -3174,7 +3234,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B5">
         <v>25.170068027210899</v>
@@ -3188,7 +3248,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3206,18 +3266,18 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -3225,7 +3285,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>1189105</v>
@@ -3239,7 +3299,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>898100</v>
@@ -3253,7 +3313,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B5">
         <v>147</v>
@@ -3267,7 +3327,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B6">
         <v>64</v>
@@ -3281,7 +3341,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B7">
         <v>438</v>
@@ -3295,7 +3355,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B8">
         <v>75.53</v>
@@ -3309,7 +3369,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3327,18 +3387,18 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -3346,7 +3406,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>1189105</v>
@@ -3360,7 +3420,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>898100</v>
@@ -3374,7 +3434,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B5">
         <v>147</v>
@@ -3388,7 +3448,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B6">
         <v>64</v>
@@ -3402,7 +3462,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B7">
         <v>438</v>
@@ -3416,7 +3476,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B8">
         <v>75.53</v>
@@ -3430,7 +3490,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3445,7 +3505,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3542,7 +3602,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3561,15 +3621,15 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -3577,7 +3637,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>1417823</v>
@@ -3588,7 +3648,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>1041199</v>
@@ -3599,7 +3659,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <v>800379</v>
@@ -3610,7 +3670,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>219670</v>
@@ -3621,7 +3681,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B7">
         <v>73.436458570639644</v>
@@ -3632,7 +3692,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3650,12 +3710,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3678,7 +3738,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B3">
         <v>1549</v>
@@ -3701,7 +3761,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B4">
         <v>340</v>
@@ -3724,7 +3784,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B5">
         <v>1209</v>
@@ -3747,7 +3807,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3765,7 +3825,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3793,7 +3853,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B3">
         <v>58909</v>
@@ -3862,7 +3922,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3880,12 +3940,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3908,7 +3968,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B3">
         <v>58909</v>
@@ -3931,7 +3991,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B4">
         <v>34464</v>
@@ -3954,7 +4014,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B5">
         <v>24445</v>
@@ -3977,7 +4037,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3995,7 +4055,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -4096,7 +4156,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -4106,50 +4166,59 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="90.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.109375" style="61" customWidth="1"/>
+    <col min="11" max="11" width="40.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.85">
       <c r="A1" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="J1" s="56"/>
+    </row>
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.85">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B3">
         <v>29</v>
@@ -4175,13 +4244,16 @@
       <c r="I3">
         <v>0.73058884914327338</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="59">
+        <v>40</v>
+      </c>
+      <c r="K3">
         <v>0.81</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -4207,13 +4279,16 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="58">
+        <v>3</v>
+      </c>
+      <c r="K4">
         <v>0.47</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -4239,13 +4314,16 @@
       <c r="I5">
         <v>0.24808313197897019</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="58">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -4271,13 +4349,16 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="58">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -4303,13 +4384,16 @@
       <c r="I7">
         <v>0.22599358099236169</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="58">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <v>0.45</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4335,13 +4419,16 @@
       <c r="I8">
         <v>0.25555205689671667</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="58">
+        <v>2</v>
+      </c>
+      <c r="K8">
         <v>0.51</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -4367,13 +4454,16 @@
       <c r="I9">
         <v>0.61746846748415452</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="58">
+        <v>4</v>
+      </c>
+      <c r="K9">
         <v>1.23</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4399,13 +4489,16 @@
       <c r="I10">
         <v>5.5848109197769196</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="58">
+        <v>1</v>
+      </c>
+      <c r="K10">
         <v>1.39</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -4431,13 +4524,16 @@
       <c r="I11">
         <v>1.626380412417151</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="58">
+        <v>5</v>
+      </c>
+      <c r="K11">
         <v>2.39</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -4463,13 +4559,16 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="58">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -4495,13 +4594,16 @@
       <c r="I13">
         <v>0.82627487403747091</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="58">
+        <v>2</v>
+      </c>
+      <c r="K13">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4527,13 +4629,16 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J14" s="58">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4559,13 +4664,16 @@
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J15" s="58">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B16">
         <v>14</v>
@@ -4591,11 +4699,17 @@
       <c r="I16">
         <v>1.451517785049202</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J16" s="58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>102</v>
-      </c>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="J19" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4612,69 +4726,69 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="N2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B3">
         <v>1871</v>
@@ -4733,7 +4847,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B4">
         <v>73</v>
@@ -4777,7 +4891,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B5">
         <v>41</v>
@@ -4821,7 +4935,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B6">
         <v>55</v>
@@ -4865,7 +4979,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B7">
         <v>31</v>
@@ -4909,7 +5023,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B8">
         <v>335</v>
@@ -4953,7 +5067,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B9">
         <v>40</v>
@@ -4997,7 +5111,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -5041,7 +5155,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B11">
         <v>427</v>
@@ -5097,7 +5211,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -5141,7 +5255,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B13">
         <v>60</v>
@@ -5185,7 +5299,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B14">
         <v>35</v>
@@ -5229,7 +5343,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -5273,7 +5387,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B16">
         <v>760</v>
@@ -5332,7 +5446,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -5354,7 +5468,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="30" x14ac:dyDescent="0.85">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5377,66 +5491,66 @@
     </row>
     <row r="2" spans="1:19" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="Q2" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B3" s="10">
         <v>760</v>
@@ -5457,7 +5571,7 @@
         <v>935</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J3" s="15">
         <v>935</v>
@@ -5466,7 +5580,7 @@
         <v>1039</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="M3" s="13">
         <v>1039</v>
@@ -5475,7 +5589,7 @@
         <v>1017</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="P3" s="13">
         <v>1017</v>
@@ -5492,7 +5606,7 @@
     </row>
     <row r="4" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B4" s="10">
         <v>102</v>
@@ -5513,7 +5627,7 @@
         <v>108</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J4" s="15">
         <v>108</v>
@@ -5522,7 +5636,7 @@
         <v>115</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="M4" s="13">
         <v>115</v>
@@ -5531,7 +5645,7 @@
         <v>108</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="P4" s="13">
         <v>108</v>
@@ -5548,7 +5662,7 @@
     </row>
     <row r="5" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B5" s="10">
         <v>422</v>
@@ -5591,7 +5705,7 @@
         <v>312</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="P5" s="13">
         <v>312</v>
@@ -5608,7 +5722,7 @@
     </row>
     <row r="6" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="10">
         <v>589</v>
@@ -5622,7 +5736,7 @@
         <v>288</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G6" s="13">
         <v>288</v>
@@ -5631,7 +5745,7 @@
         <v>444</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J6" s="15">
         <v>444</v>
@@ -5640,7 +5754,7 @@
         <v>221</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="M6" s="13">
         <v>221</v>
@@ -5649,7 +5763,7 @@
         <v>268</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="P6" s="13">
         <v>268</v>
@@ -5666,7 +5780,7 @@
     </row>
     <row r="7" spans="1:19" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B7" s="16">
         <v>0</v>
@@ -5726,7 +5840,7 @@
     </row>
     <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A9" s="19" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
